--- a/src/test_xlsx/production.xlsx
+++ b/src/test_xlsx/production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SBC\oddiville-proj\oddiville-frontend\src\test_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB88EF26-F34D-4C08-902F-351C8695AC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD65CDBD-F5D6-4618-A9B7-3B6794C6D8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{26B886F0-C47D-4879-BA7B-1F2DDA084BC0}"/>
+    <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11385" xr2:uid="{26B886F0-C47D-4879-BA7B-1F2DDA084BC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -533,6 +533,9 @@
       <c r="E3">
         <v>55</v>
       </c>
+      <c r="F3">
+        <v>40</v>
+      </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
